--- a/scripts/files/COCO AU SHEET 16926.xlsx
+++ b/scripts/files/COCO AU SHEET 16926.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87A72DAE-8E9B-4BE6-8888-19F64EDEC0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0965F8EC-3FF3-4343-8537-2AF91CFCC0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF8E7513-595A-44B7-ABA2-9D443769AEF5}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="BOOKING RELATED" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ROOM CHANGE'!$A$1:$AC$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ROOM CHANGE'!$A$1:$AC$21</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="140">
   <si>
     <t>NO.</t>
   </si>
@@ -183,325 +183,283 @@
     <t>3569</t>
   </si>
   <si>
+    <t>Navya Bajoria</t>
+  </si>
+  <si>
+    <t>navyabajoria08@gmail.com</t>
+  </si>
+  <si>
+    <t>HDFC32D7B22B35C7</t>
+  </si>
+  <si>
+    <t>ARXPB2661G</t>
+  </si>
+  <si>
+    <t>1518</t>
+  </si>
+  <si>
+    <t>Shravya Desai</t>
+  </si>
+  <si>
+    <t>shravs.0703@gmail.com</t>
+  </si>
+  <si>
+    <t>HDFC7F4109F4DBFE</t>
+  </si>
+  <si>
+    <t>LBZPD6860Q</t>
+  </si>
+  <si>
+    <t>3386</t>
+  </si>
+  <si>
+    <t>RASHI CHOUDHARY</t>
+  </si>
+  <si>
+    <t>rashi.pid25266@cept.ac.in</t>
+  </si>
+  <si>
+    <t>Without meal</t>
+  </si>
+  <si>
+    <t>INR52000/- (000212870952) INR50000/- (000204462992)</t>
+  </si>
+  <si>
+    <t>BWOPC3120J</t>
+  </si>
+  <si>
+    <t>6575</t>
+  </si>
+  <si>
+    <t>KIRTANAA MANISEKARAN</t>
+  </si>
+  <si>
+    <t>kirtanaa.pid25165@cept.ac.in</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Not Submitted</t>
+  </si>
+  <si>
+    <t>Shabana Shabana</t>
+  </si>
+  <si>
+    <t>shabana.pid25305@cept.ac.in</t>
+  </si>
+  <si>
+    <t>INR50000 (618600463907) NRI45000/- (618708583643) INR7000/-(655432567683)</t>
+  </si>
+  <si>
+    <t>MQHPS3403E</t>
+  </si>
+  <si>
+    <t>5477</t>
+  </si>
+  <si>
+    <t>VIDYA HARISH RUPARELIA</t>
+  </si>
+  <si>
+    <t>vidyavr2573@gmail.com</t>
+  </si>
+  <si>
+    <t>INR102000/-(618408000000) INR24000/- (619787208866)</t>
+  </si>
+  <si>
+    <t>Nabanita Chakravarty</t>
+  </si>
+  <si>
+    <t>anujchakravarty@rediffmail.com</t>
+  </si>
+  <si>
+    <t>618000000000</t>
+  </si>
+  <si>
+    <t>Gauri Parate</t>
+  </si>
+  <si>
+    <t>gauriparate02@gmail.com</t>
+  </si>
+  <si>
+    <t>INR37000/-(JOAV9MPN5984) INR15000/- (VL0G1NWB4914) INR50000/- (O613SEX11397)</t>
+  </si>
+  <si>
+    <t>2486</t>
+  </si>
+  <si>
+    <t>Rahini Kishor Naik</t>
+  </si>
+  <si>
+    <t>rahininaik04@gmail.com</t>
+  </si>
+  <si>
+    <t>1319</t>
+  </si>
+  <si>
+    <t>LALLAWMKIMI CHENKUAL</t>
+  </si>
+  <si>
+    <t>lallawmkimi2001@gmail.com</t>
+  </si>
+  <si>
+    <t>INR100000/- (620120976562) INR26000/- (656733167469)</t>
+  </si>
+  <si>
+    <t>CCYPC6873P</t>
+  </si>
+  <si>
+    <t>8957</t>
+  </si>
+  <si>
+    <t>Ridhima Agarwal</t>
+  </si>
+  <si>
+    <t>ridhima.agarwal.2008@gmail.com</t>
+  </si>
+  <si>
+    <t>INR50000/-(618500677119) INR50000/- (FTIMPS173420) INR10000/- (FTIMPS173387) INR16000/- (618500829553)</t>
+  </si>
+  <si>
+    <t>GNZPA8986F</t>
+  </si>
+  <si>
+    <t>5991</t>
+  </si>
+  <si>
+    <t>SHRUTI SINGH</t>
+  </si>
+  <si>
+    <t>ss.shruti.1502@gmail.com</t>
+  </si>
+  <si>
+    <t>INR50000/- (618422888267) INR50000/-(618508502094) INR2000/- (T2607040853023844618574)</t>
+  </si>
+  <si>
+    <t>NZOPS0776K</t>
+  </si>
+  <si>
+    <t>0142</t>
+  </si>
+  <si>
+    <t>Manveen Kaur</t>
+  </si>
+  <si>
+    <t>manveentheleo@gmail.com</t>
+  </si>
+  <si>
+    <t>INR15000/- (000141784991) INR87000/- (000408385608)</t>
+  </si>
+  <si>
+    <t>Suditi Tewari</t>
+  </si>
+  <si>
+    <t>sudititewari07@gmail.com</t>
+  </si>
+  <si>
+    <t>INR94000/- (619401051421) INR15000/- (619412673077)</t>
+  </si>
+  <si>
+    <t>CZKPT8790F</t>
+  </si>
+  <si>
+    <t>2351</t>
+  </si>
+  <si>
+    <t>Vidhi Rohilla</t>
+  </si>
+  <si>
+    <t>vidhi.rohila3@gmail.com</t>
+  </si>
+  <si>
+    <t>INR25000/- (621780744794) INR75000/- (621780695616) INR26000/- (621782092226)</t>
+  </si>
+  <si>
+    <t>Meher Sana Vinay</t>
+  </si>
+  <si>
+    <t>mehersana687@gmail.com</t>
+  </si>
+  <si>
+    <t>INR50000/- (000496699545) INR76000/- (HDFC6CE5FCA7475A)</t>
+  </si>
+  <si>
+    <t>JCKPM8795K</t>
+  </si>
+  <si>
+    <t>7083</t>
+  </si>
+  <si>
+    <t>Samina Tinwala</t>
+  </si>
+  <si>
+    <t>saminatinwala2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Double Sharing</t>
+  </si>
+  <si>
+    <t>INR15000/- BANK DEPOSIT INR940000/- (000000000063)</t>
+  </si>
+  <si>
+    <t>Urvi Meera Srinivasan</t>
+  </si>
+  <si>
+    <t>umeerasrinivasan@gmail.com</t>
+  </si>
+  <si>
+    <t>Devashi Paliwal</t>
+  </si>
+  <si>
+    <t>devashipaliwal008@gmail.com</t>
+  </si>
+  <si>
+    <t>1+2</t>
+  </si>
+  <si>
+    <t>Included in rental</t>
+  </si>
+  <si>
+    <t>31st May 2027</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Non Cept</t>
+  </si>
+  <si>
+    <t>draft_submitted</t>
+  </si>
+  <si>
     <t>Hiya Nagori</t>
   </si>
   <si>
     <t>hiyanagori125@gmail.com</t>
   </si>
   <si>
-    <t>1+2</t>
-  </si>
-  <si>
-    <t>Included in rental</t>
-  </si>
-  <si>
-    <t>31st May 2027</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t>Non Cept</t>
-  </si>
-  <si>
-    <t>Navya Bajoria</t>
-  </si>
-  <si>
-    <t>navyabajoria08@gmail.com</t>
-  </si>
-  <si>
-    <t>HDFC32D7B22B35C7</t>
-  </si>
-  <si>
-    <t>ARXPB2661G</t>
-  </si>
-  <si>
-    <t>1518</t>
-  </si>
-  <si>
-    <t>Shravya Desai</t>
-  </si>
-  <si>
-    <t>shravs.0703@gmail.com</t>
-  </si>
-  <si>
-    <t>HDFC7F4109F4DBFE</t>
-  </si>
-  <si>
-    <t>LBZPD6860Q</t>
-  </si>
-  <si>
-    <t>3386</t>
-  </si>
-  <si>
-    <t>RASHI CHOUDHARY</t>
-  </si>
-  <si>
-    <t>rashi.pid25266@cept.ac.in</t>
-  </si>
-  <si>
-    <t>Without meal</t>
-  </si>
-  <si>
-    <t>INR52000/- (000212870952) INR50000/- (000204462992)</t>
-  </si>
-  <si>
-    <t>BWOPC3120J</t>
-  </si>
-  <si>
-    <t>6575</t>
-  </si>
-  <si>
-    <t>KIRTANAA MANISEKARAN</t>
-  </si>
-  <si>
-    <t>kirtanaa.pid25165@cept.ac.in</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Not Submitted</t>
-  </si>
-  <si>
-    <t>Shabana Shabana</t>
-  </si>
-  <si>
-    <t>shabana.pid25305@cept.ac.in</t>
-  </si>
-  <si>
-    <t>INR50000 (618600463907) NRI45000/- (618708583643) INR7000/-(655432567683)</t>
-  </si>
-  <si>
-    <t>MQHPS3403E</t>
-  </si>
-  <si>
-    <t>5477</t>
-  </si>
-  <si>
-    <t>VIDYA HARISH RUPARELIA</t>
-  </si>
-  <si>
-    <t>vidyavr2573@gmail.com</t>
-  </si>
-  <si>
-    <t>INR102000/-(618408000000) INR24000/- (619787208866)</t>
-  </si>
-  <si>
-    <t>Nabanita Chakravarty</t>
-  </si>
-  <si>
-    <t>anujchakravarty@rediffmail.com</t>
-  </si>
-  <si>
-    <t>618000000000</t>
-  </si>
-  <si>
-    <t>Gauri Parate</t>
-  </si>
-  <si>
-    <t>gauriparate02@gmail.com</t>
-  </si>
-  <si>
-    <t>INR37000/-(JOAV9MPN5984) INR15000/- (VL0G1NWB4914) INR50000/- (O613SEX11397)</t>
-  </si>
-  <si>
-    <t>2486</t>
-  </si>
-  <si>
-    <t>Rahini Kishor Naik</t>
-  </si>
-  <si>
-    <t>rahininaik04@gmail.com</t>
-  </si>
-  <si>
-    <t>1319</t>
-  </si>
-  <si>
-    <t>LALLAWMKIMI CHENKUAL</t>
-  </si>
-  <si>
-    <t>lallawmkimi2001@gmail.com</t>
-  </si>
-  <si>
-    <t>INR100000/- (620120976562) INR26000/- (656733167469)</t>
-  </si>
-  <si>
-    <t>CCYPC6873P</t>
-  </si>
-  <si>
-    <t>8957</t>
-  </si>
-  <si>
-    <t>Ridhima Agarwal</t>
-  </si>
-  <si>
-    <t>ridhima.agarwal.2008@gmail.com</t>
-  </si>
-  <si>
-    <t>INR50000/-(618500677119) INR50000/- (FTIMPS173420) INR10000/- (FTIMPS173387) INR16000/- (618500829553)</t>
-  </si>
-  <si>
-    <t>GNZPA8986F</t>
-  </si>
-  <si>
-    <t>5991</t>
-  </si>
-  <si>
-    <t>Sermistha Singh</t>
-  </si>
-  <si>
-    <t>harshitapanwaar@gmail.com</t>
-  </si>
-  <si>
-    <t>Double Sharing</t>
-  </si>
-  <si>
-    <t>QXYPS0230P</t>
-  </si>
-  <si>
-    <t>not-verified</t>
+    <t>Surat Sarup</t>
+  </si>
+  <si>
+    <t>surat.sarup@gmail.com</t>
+  </si>
+  <si>
+    <t>draft_booking</t>
+  </si>
+  <si>
+    <t>Ajab Poonawala</t>
+  </si>
+  <si>
+    <t>ajabpoonawala07@gmail.com</t>
+  </si>
+  <si>
+    <t>17th July 2026</t>
   </si>
   <si>
     <t>Radha Patel</t>
   </si>
   <si>
     <t>radhapatel250405@gamil.com</t>
-  </si>
-  <si>
-    <t>SHRUTI SINGH</t>
-  </si>
-  <si>
-    <t>ss.shruti.1502@gmail.com</t>
-  </si>
-  <si>
-    <t>INR50000/- (618422888267) INR50000/-(618508502094) INR2000/- (T2607040853023844618574)</t>
-  </si>
-  <si>
-    <t>NZOPS0776K</t>
-  </si>
-  <si>
-    <t>0142</t>
-  </si>
-  <si>
-    <t>Manveen Kaur</t>
-  </si>
-  <si>
-    <t>manveentheleo@gmail.com</t>
-  </si>
-  <si>
-    <t>INR15000/- (000141784991) INR87000/- (000408385608)</t>
-  </si>
-  <si>
-    <t>Devi abirami Murugappan</t>
-  </si>
-  <si>
-    <t>meenamurugappan22@gmail.com</t>
-  </si>
-  <si>
-    <t>HDFC509F54A2405A</t>
-  </si>
-  <si>
-    <t>ANNPM5354R</t>
-  </si>
-  <si>
-    <t>7575</t>
-  </si>
-  <si>
-    <t>Suditi Tewari</t>
-  </si>
-  <si>
-    <t>sudititewari07@gmail.com</t>
-  </si>
-  <si>
-    <t>INR94000/- (619401051421) INR15000/- (619412673077)</t>
-  </si>
-  <si>
-    <t>CZKPT8790F</t>
-  </si>
-  <si>
-    <t>2351</t>
-  </si>
-  <si>
-    <t>Vidhi Rohilla</t>
-  </si>
-  <si>
-    <t>vidhi.rohila3@gmail.com</t>
-  </si>
-  <si>
-    <t>INR25000/- (621780744794) INR75000/- (621780695616) INR26000/- (621782092226)</t>
-  </si>
-  <si>
-    <t>Meher Sana Vinay</t>
-  </si>
-  <si>
-    <t>mehersana687@gmail.com</t>
-  </si>
-  <si>
-    <t>INR50000/- (000496699545) INR76000/- (HDFC6CE5FCA7475A)</t>
-  </si>
-  <si>
-    <t>JCKPM8795K</t>
-  </si>
-  <si>
-    <t>7083</t>
-  </si>
-  <si>
-    <t>Samina Tinwala</t>
-  </si>
-  <si>
-    <t>saminatinwala2008@gmail.com</t>
-  </si>
-  <si>
-    <t>INR15000/- BANK DEPOSIT INR940000/- (000000000063)</t>
-  </si>
-  <si>
-    <t>Sanjana Shah</t>
-  </si>
-  <si>
-    <t>sanjanashah2512@gmail.com</t>
-  </si>
-  <si>
-    <t>Inr100000/- (OA6F0XJB2006) INR33000 (CNEOG4FF1508)</t>
-  </si>
-  <si>
-    <t>OOLPS0077A</t>
-  </si>
-  <si>
-    <t>0245</t>
-  </si>
-  <si>
-    <t>Urvi Meera Srinivasan</t>
-  </si>
-  <si>
-    <t>umeerasrinivasan@gmail.com</t>
-  </si>
-  <si>
-    <t>Devashi Paliwal</t>
-  </si>
-  <si>
-    <t>devashipaliwal008@gmail.com</t>
-  </si>
-  <si>
-    <t>draft_submitted</t>
-  </si>
-  <si>
-    <t>Surat Sarup</t>
-  </si>
-  <si>
-    <t>surat.sarup@gmail.com</t>
-  </si>
-  <si>
-    <t>draft_booking</t>
-  </si>
-  <si>
-    <t>Ajab Poonawala</t>
-  </si>
-  <si>
-    <t>ajabpoonawala07@gmail.com</t>
-  </si>
-  <si>
-    <t>17th July 2026</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{743C4FE5-64DA-483F-B448-7F41521E26D2}">
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1384,112 +1342,112 @@
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="7">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E4" s="9">
-        <v>9024003868</v>
+        <v>9831070908</v>
       </c>
       <c r="F4" s="10">
-        <v>111</v>
-      </c>
-      <c r="G4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H4" s="30" t="e">
-        <v>#N/A</v>
+        <v>115</v>
+      </c>
+      <c r="G4" s="7">
+        <v>309</v>
+      </c>
+      <c r="H4" s="30" t="b">
+        <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J4" s="9">
-        <v>67500</v>
-      </c>
-      <c r="K4" s="9">
-        <v>5000</v>
-      </c>
-      <c r="L4" s="9" t="s">
+        <v>126000</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="8">
+        <v>15000</v>
+      </c>
+      <c r="N4" s="8">
+        <v>87000</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" s="9">
+        <v>24000</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="11">
+        <v>46221</v>
+      </c>
+      <c r="T4" s="11"/>
+      <c r="U4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="9">
-        <v>22000</v>
-      </c>
-      <c r="N4" s="9">
-        <v>17000</v>
-      </c>
-      <c r="O4" s="9">
-        <v>22000</v>
-      </c>
-      <c r="P4" s="8" t="s">
+      <c r="V4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="X4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="R4" s="9">
-        <v>1500</v>
-      </c>
-      <c r="S4" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T4" s="15">
-        <v>46232</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="W4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB4" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC4" s="30"/>
+      <c r="Z4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="5" spans="1:29">
       <c r="A5" s="7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="9">
-        <v>9831070908</v>
+        <v>7021151035</v>
       </c>
       <c r="F5" s="10">
         <v>115</v>
       </c>
       <c r="G5" s="7">
-        <v>309</v>
+        <v>213</v>
       </c>
       <c r="H5" s="30" t="b">
         <v>0</v>
@@ -1525,23 +1483,23 @@
         <v>0</v>
       </c>
       <c r="S5" s="11">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="T5" s="11"/>
       <c r="U5" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="V5" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="X5" s="7" t="s">
         <v>37</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Z5" s="7" t="s">
         <v>37</v>
@@ -1558,25 +1516,25 @@
     </row>
     <row r="6" spans="1:29">
       <c r="A6" s="7">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="9">
-        <v>7021151035</v>
-      </c>
-      <c r="F6" s="10">
-        <v>115</v>
+        <v>6265107748</v>
+      </c>
+      <c r="F6" s="12">
+        <v>203</v>
       </c>
       <c r="G6" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H6" s="30" t="b">
         <v>0</v>
@@ -1585,7 +1543,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="9">
-        <v>126000</v>
+        <v>102000</v>
       </c>
       <c r="K6" s="8">
         <v>0</v>
@@ -1602,8 +1560,8 @@
       <c r="O6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="9">
-        <v>24000</v>
+      <c r="P6" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="Q6" s="8" t="s">
         <v>33</v>
@@ -1612,23 +1570,23 @@
         <v>0</v>
       </c>
       <c r="S6" s="11">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V6" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X6" s="7" t="s">
         <v>37</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="7" t="s">
         <v>37</v>
@@ -1645,19 +1603,19 @@
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E7" s="9">
-        <v>6265107748</v>
+        <v>9483285811</v>
       </c>
       <c r="F7" s="12">
         <v>203</v>
@@ -1690,7 +1648,7 @@
         <v>33</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>33</v>
@@ -1702,23 +1660,23 @@
         <v>46219</v>
       </c>
       <c r="T7" s="11"/>
-      <c r="U7" s="9" t="s">
-        <v>67</v>
+      <c r="U7" s="13">
+        <v>620000000000</v>
       </c>
       <c r="V7" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>39</v>
@@ -1732,19 +1690,19 @@
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E8" s="9">
-        <v>9483285811</v>
+        <v>7356004041</v>
       </c>
       <c r="F8" s="12">
         <v>203</v>
@@ -1777,7 +1735,7 @@
         <v>33</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="8" t="s">
         <v>33</v>
@@ -1786,26 +1744,26 @@
         <v>0</v>
       </c>
       <c r="S8" s="11">
-        <v>46219</v>
+        <v>46214</v>
       </c>
       <c r="T8" s="11"/>
-      <c r="U8" s="13">
-        <v>620000000000</v>
+      <c r="U8" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="V8" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AA8" s="7" t="s">
         <v>39</v>
@@ -1819,25 +1777,25 @@
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="7">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="9">
-        <v>7356004041</v>
+        <v>9429048096</v>
       </c>
       <c r="F9" s="12">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G9" s="7">
-        <v>215</v>
+        <v>102</v>
       </c>
       <c r="H9" s="30" t="b">
         <v>0</v>
@@ -1846,7 +1804,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="9">
-        <v>102000</v>
+        <v>126000</v>
       </c>
       <c r="K9" s="8">
         <v>0</v>
@@ -1863,8 +1821,8 @@
       <c r="O9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P9" s="9" t="s">
-        <v>66</v>
+      <c r="P9" s="9">
+        <v>24000</v>
       </c>
       <c r="Q9" s="8" t="s">
         <v>33</v>
@@ -1873,26 +1831,26 @@
         <v>0</v>
       </c>
       <c r="S9" s="11">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V9" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="AA9" s="7" t="s">
         <v>39</v>
@@ -1906,25 +1864,25 @@
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" s="9">
-        <v>9429048096</v>
+        <v>7093503319</v>
       </c>
       <c r="F10" s="12">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G10" s="7">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="H10" s="30" t="b">
         <v>0</v>
@@ -1960,26 +1918,26 @@
         <v>0</v>
       </c>
       <c r="S10" s="11">
-        <v>46213</v>
+        <v>46223</v>
       </c>
       <c r="T10" s="11"/>
-      <c r="U10" s="9" t="s">
-        <v>81</v>
+      <c r="U10" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="V10" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AA10" s="7" t="s">
         <v>39</v>
@@ -1993,19 +1951,19 @@
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E11" s="9">
-        <v>7093503319</v>
+        <v>9136347960</v>
       </c>
       <c r="F11" s="12">
         <v>215</v>
@@ -2020,7 +1978,7 @@
         <v>31</v>
       </c>
       <c r="J11" s="9">
-        <v>126000</v>
+        <v>102000</v>
       </c>
       <c r="K11" s="8">
         <v>0</v>
@@ -2037,8 +1995,8 @@
       <c r="O11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P11" s="9">
-        <v>24000</v>
+      <c r="P11" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="Q11" s="8" t="s">
         <v>33</v>
@@ -2050,23 +2008,23 @@
         <v>46223</v>
       </c>
       <c r="T11" s="11"/>
-      <c r="U11" s="17" t="s">
-        <v>84</v>
+      <c r="U11" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="V11" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>39</v>
@@ -2080,19 +2038,19 @@
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E12" s="9">
-        <v>9136347960</v>
+        <v>9324488709</v>
       </c>
       <c r="F12" s="12">
         <v>215</v>
@@ -2107,7 +2065,7 @@
         <v>31</v>
       </c>
       <c r="J12" s="9">
-        <v>102000</v>
+        <v>138000</v>
       </c>
       <c r="K12" s="8">
         <v>0</v>
@@ -2124,8 +2082,8 @@
       <c r="O12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="9" t="s">
-        <v>66</v>
+      <c r="P12" s="9">
+        <v>36000</v>
       </c>
       <c r="Q12" s="8" t="s">
         <v>33</v>
@@ -2137,20 +2095,20 @@
         <v>46223</v>
       </c>
       <c r="T12" s="11"/>
-      <c r="U12" s="9" t="s">
-        <v>87</v>
+      <c r="U12" s="17" t="s">
+        <v>77</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Z12" s="7" t="s">
         <v>37</v>
@@ -2167,25 +2125,25 @@
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="7">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="9">
-        <v>9324488709</v>
-      </c>
-      <c r="F13" s="12">
-        <v>215</v>
+      <c r="C13" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="18">
+        <v>9972617158</v>
+      </c>
+      <c r="F13" s="10">
+        <v>307</v>
       </c>
       <c r="G13" s="7">
-        <v>203</v>
+        <v>314</v>
       </c>
       <c r="H13" s="30" t="b">
         <v>0</v>
@@ -2194,7 +2152,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="9">
-        <v>138000</v>
+        <v>126000</v>
       </c>
       <c r="K13" s="8">
         <v>0</v>
@@ -2212,7 +2170,7 @@
         <v>33</v>
       </c>
       <c r="P13" s="9">
-        <v>36000</v>
+        <v>24000</v>
       </c>
       <c r="Q13" s="8" t="s">
         <v>33</v>
@@ -2221,23 +2179,23 @@
         <v>0</v>
       </c>
       <c r="S13" s="11">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="T13" s="11"/>
-      <c r="U13" s="17" t="s">
-        <v>84</v>
+      <c r="U13" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="V13" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Z13" s="7" t="s">
         <v>37</v>
@@ -2254,25 +2212,25 @@
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="18">
-        <v>9972617158</v>
+      <c r="C14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="9">
+        <v>9599120093</v>
       </c>
       <c r="F14" s="10">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G14" s="7">
-        <v>314</v>
+        <v>115</v>
       </c>
       <c r="H14" s="30" t="b">
         <v>0</v>
@@ -2308,23 +2266,23 @@
         <v>0</v>
       </c>
       <c r="S14" s="11">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="T14" s="11"/>
       <c r="U14" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="V14" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="X14" s="7" t="s">
         <v>37</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Z14" s="7" t="s">
         <v>37</v>
@@ -2341,25 +2299,25 @@
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="7">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E15" s="9">
-        <v>9599120093</v>
-      </c>
-      <c r="F15" s="10">
-        <v>309</v>
+        <v>9978557837</v>
+      </c>
+      <c r="F15" s="12">
+        <v>401</v>
       </c>
       <c r="G15" s="7">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="H15" s="30" t="b">
         <v>0</v>
@@ -2368,7 +2326,7 @@
         <v>31</v>
       </c>
       <c r="J15" s="9">
-        <v>126000</v>
+        <v>102000</v>
       </c>
       <c r="K15" s="8">
         <v>0</v>
@@ -2385,8 +2343,8 @@
       <c r="O15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P15" s="9">
-        <v>24000</v>
+      <c r="P15" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="Q15" s="8" t="s">
         <v>33</v>
@@ -2395,23 +2353,23 @@
         <v>0</v>
       </c>
       <c r="S15" s="11">
-        <v>46223</v>
+        <v>46214</v>
       </c>
       <c r="T15" s="11"/>
       <c r="U15" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="V15" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="X15" s="7" t="s">
         <v>37</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="Z15" s="7" t="s">
         <v>37</v>
@@ -2428,85 +2386,83 @@
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="7">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="9">
+        <v>9912529016</v>
+      </c>
+      <c r="F16" s="12">
+        <v>405</v>
+      </c>
+      <c r="G16" s="7">
+        <v>307</v>
+      </c>
+      <c r="H16" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="9">
+        <v>102000</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="8">
+        <v>15000</v>
+      </c>
+      <c r="N16" s="8">
+        <v>87000</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0</v>
+      </c>
+      <c r="S16" s="11">
+        <v>46221</v>
+      </c>
+      <c r="T16" s="11"/>
+      <c r="U16" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="9">
-        <v>7814304969</v>
-      </c>
-      <c r="F16" s="12">
-        <v>310</v>
-      </c>
-      <c r="G16" s="7">
-        <v>301</v>
-      </c>
-      <c r="H16" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="9">
-        <v>55166</v>
-      </c>
-      <c r="K16" s="9">
-        <v>3000</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M16" s="9">
-        <v>23000</v>
-      </c>
-      <c r="N16" s="9">
-        <v>4666</v>
-      </c>
-      <c r="O16" s="9">
-        <v>23000</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R16" s="9">
-        <v>1500</v>
-      </c>
-      <c r="S16" s="11">
-        <v>46193</v>
-      </c>
-      <c r="T16" s="15">
-        <v>46193</v>
-      </c>
-      <c r="U16" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="V16" s="8" t="s">
-        <v>53</v>
+      <c r="V16" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="W16" s="7" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="Y16" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA16" s="7" t="e">
-        <v>#N/A</v>
+        <v>66</v>
+      </c>
+      <c r="AA16" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="AB16" s="7" t="s">
         <v>40</v>
@@ -2517,112 +2473,112 @@
     </row>
     <row r="17" spans="1:29">
       <c r="A17" s="7">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>107</v>
+      <c r="C17" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E17" s="9">
-        <v>7778910113</v>
-      </c>
-      <c r="F17" s="12">
-        <v>314</v>
-      </c>
-      <c r="G17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H17" s="30" t="e">
-        <v>#N/A</v>
+        <v>9999743322</v>
+      </c>
+      <c r="F17" s="10">
+        <v>410</v>
+      </c>
+      <c r="G17" s="7">
+        <v>411</v>
+      </c>
+      <c r="H17" s="30" t="b">
+        <v>0</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J17" s="9">
-        <v>63000</v>
-      </c>
-      <c r="K17" s="9">
-        <v>3500</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M17" s="9">
-        <v>20500</v>
-      </c>
-      <c r="N17" s="9">
-        <v>17000</v>
-      </c>
-      <c r="O17" s="9">
-        <v>20500</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>50</v>
+        <v>109000</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="8">
+        <v>15000</v>
+      </c>
+      <c r="N17" s="8">
+        <v>94000</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R17" s="9">
-        <v>1500</v>
-      </c>
-      <c r="S17" s="11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T17" s="15">
-        <v>38932</v>
-      </c>
-      <c r="U17" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="V17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="W17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB17" s="7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC17" s="30"/>
+        <v>33</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0</v>
+      </c>
+      <c r="S17" s="11">
+        <v>46218</v>
+      </c>
+      <c r="T17" s="11"/>
+      <c r="U17" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="X17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC17" s="30" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18" spans="1:29">
       <c r="A18" s="7">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="9">
-        <v>9978557837</v>
+      <c r="E18" s="21">
+        <v>9971509006</v>
       </c>
       <c r="F18" s="12">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="G18" s="7">
-        <v>103</v>
+        <v>414</v>
       </c>
       <c r="H18" s="30" t="b">
         <v>0</v>
@@ -2631,7 +2587,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="9">
-        <v>102000</v>
+        <v>126000</v>
       </c>
       <c r="K18" s="8">
         <v>0</v>
@@ -2648,8 +2604,8 @@
       <c r="O18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P18" s="9" t="s">
-        <v>66</v>
+      <c r="P18" s="9">
+        <v>24000</v>
       </c>
       <c r="Q18" s="8" t="s">
         <v>33</v>
@@ -2658,26 +2614,26 @@
         <v>0</v>
       </c>
       <c r="S18" s="11">
-        <v>46214</v>
+        <v>46222</v>
       </c>
       <c r="T18" s="11"/>
       <c r="U18" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V18" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W18" s="7" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="X18" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="Y18" s="7" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="AA18" s="7" t="s">
         <v>39</v>
@@ -2691,25 +2647,25 @@
     </row>
     <row r="19" spans="1:29">
       <c r="A19" s="7">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="9">
+        <v>8850419415</v>
+      </c>
+      <c r="F19" s="10">
+        <v>414</v>
+      </c>
+      <c r="G19" s="7">
         <v>115</v>
-      </c>
-      <c r="E19" s="9">
-        <v>9912529016</v>
-      </c>
-      <c r="F19" s="12">
-        <v>405</v>
-      </c>
-      <c r="G19" s="7">
-        <v>307</v>
       </c>
       <c r="H19" s="30" t="b">
         <v>0</v>
@@ -2718,7 +2674,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="9">
-        <v>102000</v>
+        <v>126000</v>
       </c>
       <c r="K19" s="8">
         <v>0</v>
@@ -2735,8 +2691,8 @@
       <c r="O19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P19" s="9" t="s">
-        <v>66</v>
+      <c r="P19" s="9">
+        <v>24000</v>
       </c>
       <c r="Q19" s="8" t="s">
         <v>33</v>
@@ -2745,26 +2701,26 @@
         <v>0</v>
       </c>
       <c r="S19" s="11">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="T19" s="11"/>
       <c r="U19" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="V19" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>39</v>
@@ -2778,34 +2734,34 @@
     </row>
     <row r="20" spans="1:29">
       <c r="A20" s="7">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9">
+        <v>9109594107</v>
+      </c>
+      <c r="F20" s="12">
+        <v>415</v>
+      </c>
+      <c r="G20" s="7">
+        <v>507</v>
+      </c>
+      <c r="H20" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="9">
-        <v>9384158303</v>
-      </c>
-      <c r="F20" s="12">
-        <v>409</v>
-      </c>
-      <c r="G20" s="7">
-        <v>405</v>
-      </c>
-      <c r="H20" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="J20" s="9">
-        <v>126000</v>
+        <v>109000</v>
       </c>
       <c r="K20" s="8">
         <v>0</v>
@@ -2817,13 +2773,13 @@
         <v>15000</v>
       </c>
       <c r="N20" s="8">
-        <v>87000</v>
+        <v>94000</v>
       </c>
       <c r="O20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P20" s="9">
-        <v>24000</v>
+      <c r="P20" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="Q20" s="8" t="s">
         <v>33</v>
@@ -2832,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="11">
-        <v>46222</v>
+        <v>46220</v>
       </c>
       <c r="T20" s="11"/>
       <c r="U20" s="9" t="s">
@@ -2842,16 +2798,16 @@
         <v>35</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="Y20" s="7" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="AA20" s="7" t="s">
         <v>39</v>
@@ -2865,34 +2821,34 @@
     </row>
     <row r="21" spans="1:29">
       <c r="A21" s="7">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E21" s="9">
-        <v>9999743322</v>
+        <v>7625080154</v>
       </c>
       <c r="F21" s="10">
-        <v>410</v>
+        <v>507</v>
       </c>
       <c r="G21" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H21" s="30" t="b">
         <v>0</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="J21" s="9">
-        <v>109000</v>
+        <v>133000</v>
       </c>
       <c r="K21" s="8">
         <v>0</v>
@@ -2909,8 +2865,8 @@
       <c r="O21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="P21" s="9" t="s">
-        <v>66</v>
+      <c r="P21" s="9">
+        <v>24000</v>
       </c>
       <c r="Q21" s="8" t="s">
         <v>33</v>
@@ -2919,26 +2875,26 @@
         <v>0</v>
       </c>
       <c r="S21" s="11">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="T21" s="11"/>
-      <c r="U21" s="9" t="s">
-        <v>124</v>
+      <c r="U21" s="9">
+        <v>126194463522227</v>
       </c>
       <c r="V21" s="9" t="s">
         <v>35</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="X21" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="Y21" s="7" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>39</v>
@@ -2950,448 +2906,13 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:29">
-      <c r="A22" s="7">
-        <v>155</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="21">
-        <v>9971509006</v>
-      </c>
-      <c r="F22" s="12">
-        <v>411</v>
-      </c>
-      <c r="G22" s="7">
-        <v>414</v>
-      </c>
-      <c r="H22" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="9">
-        <v>126000</v>
-      </c>
-      <c r="K22" s="8">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="8">
-        <v>15000</v>
-      </c>
-      <c r="N22" s="8">
-        <v>87000</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P22" s="9">
-        <v>24000</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R22" s="8">
-        <v>0</v>
-      </c>
-      <c r="S22" s="11">
-        <v>46222</v>
-      </c>
-      <c r="T22" s="11"/>
-      <c r="U22" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="V22" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="X22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z22" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC22" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
-      <c r="A23" s="7">
-        <v>164</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="9">
-        <v>8850419415</v>
-      </c>
-      <c r="F23" s="10">
-        <v>414</v>
-      </c>
-      <c r="G23" s="7">
-        <v>115</v>
-      </c>
-      <c r="H23" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="9">
-        <v>126000</v>
-      </c>
-      <c r="K23" s="8">
-        <v>0</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M23" s="8">
-        <v>15000</v>
-      </c>
-      <c r="N23" s="8">
-        <v>87000</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P23" s="9">
-        <v>24000</v>
-      </c>
-      <c r="Q23" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R23" s="8">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11">
-        <v>46223</v>
-      </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="V23" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="X23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y23" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC23" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
-      <c r="A24" s="7">
-        <v>168</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="9">
-        <v>9109594107</v>
-      </c>
-      <c r="F24" s="12">
-        <v>415</v>
-      </c>
-      <c r="G24" s="7">
-        <v>507</v>
-      </c>
-      <c r="H24" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="9">
-        <v>109000</v>
-      </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M24" s="8">
-        <v>15000</v>
-      </c>
-      <c r="N24" s="8">
-        <v>94000</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R24" s="8">
-        <v>0</v>
-      </c>
-      <c r="S24" s="11">
-        <v>46220</v>
-      </c>
-      <c r="T24" s="11"/>
-      <c r="U24" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="V24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="X24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y24" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC24" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
-      <c r="A25" s="7">
-        <v>176</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" s="9">
-        <v>6355116180</v>
-      </c>
-      <c r="F25" s="12">
-        <v>504</v>
-      </c>
-      <c r="G25" s="7">
-        <v>213</v>
-      </c>
-      <c r="H25" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="9">
-        <v>133000</v>
-      </c>
-      <c r="K25" s="8">
-        <v>0</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" s="8">
-        <v>15000</v>
-      </c>
-      <c r="N25" s="8">
-        <v>94000</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P25" s="9">
-        <v>24000</v>
-      </c>
-      <c r="Q25" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="8">
-        <v>0</v>
-      </c>
-      <c r="S25" s="11">
-        <v>46213</v>
-      </c>
-      <c r="T25" s="11"/>
-      <c r="U25" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W25" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="X25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y25" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC25" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
-      <c r="A26" s="7">
-        <v>182</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="9">
-        <v>7625080154</v>
-      </c>
-      <c r="F26" s="10">
-        <v>507</v>
-      </c>
-      <c r="G26" s="7">
-        <v>415</v>
-      </c>
-      <c r="H26" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J26" s="9">
-        <v>133000</v>
-      </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="8">
-        <v>15000</v>
-      </c>
-      <c r="N26" s="8">
-        <v>94000</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P26" s="9">
-        <v>24000</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R26" s="8">
-        <v>0</v>
-      </c>
-      <c r="S26" s="11">
-        <v>46223</v>
-      </c>
-      <c r="T26" s="11"/>
-      <c r="U26" s="9">
-        <v>126194463522227</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="W26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="X26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB26" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC26" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AC26" xr:uid="{743C4FE5-64DA-483F-B448-7F41521E26D2}"/>
-  <conditionalFormatting sqref="C1:C26">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <autoFilter ref="A1:AC21" xr:uid="{743C4FE5-64DA-483F-B448-7F41521E26D2}"/>
+  <conditionalFormatting sqref="C1:C21">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D14" r:id="rId1" xr:uid="{B6B97332-180B-49E3-90C5-54DF884D0D5A}"/>
+    <hyperlink ref="D13" r:id="rId1" xr:uid="{B6B97332-180B-49E3-90C5-54DF884D0D5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3500,10 +3021,10 @@
         <v>28</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E2" s="9">
         <v>7597534496</v>
@@ -3527,7 +3048,7 @@
         <v>5000</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="M2" s="9">
         <v>19999</v>
@@ -3539,10 +3060,10 @@
         <v>19999</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="R2" s="9">
         <v>1500</v>
@@ -3554,10 +3075,10 @@
         <v>46235</v>
       </c>
       <c r="U2" s="16" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="V2" s="8" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="W2" s="7" t="e">
         <v>#N/A</v>
@@ -3575,7 +3096,7 @@
         <v>#N/A</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:28">
@@ -3586,10 +3107,10 @@
         <v>28</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E3" s="9">
         <v>9024003868</v>
@@ -3613,7 +3134,7 @@
         <v>5000</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="M3" s="9">
         <v>22000</v>
@@ -3625,10 +3146,10 @@
         <v>22000</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="R3" s="9">
         <v>1500</v>
@@ -3640,10 +3161,10 @@
         <v>46232</v>
       </c>
       <c r="U3" s="16" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="W3" s="7" t="e">
         <v>#N/A</v>
@@ -3672,10 +3193,10 @@
         <v>28</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E4" s="9">
         <v>7666526626</v>
@@ -3745,7 +3266,7 @@
         <v>#N/A</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="43.15">
@@ -3756,10 +3277,10 @@
         <v>28</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="E5" s="9">
         <v>9979388155</v>
@@ -3783,7 +3304,7 @@
         <v>3000</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="M5" s="9">
         <v>20000</v>
@@ -3795,10 +3316,10 @@
         <v>20000</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="R5" s="9">
         <v>1500</v>
@@ -3807,13 +3328,13 @@
         <v>#N/A</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="U5" s="16" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="W5" s="7" t="e">
         <v>#N/A</v>
@@ -3842,10 +3363,10 @@
         <v>28</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="E6" s="9">
         <v>7778910113</v>
@@ -3869,7 +3390,7 @@
         <v>3500</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="M6" s="9">
         <v>20500</v>
@@ -3881,10 +3402,10 @@
         <v>20500</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="R6" s="9">
         <v>1500</v>
@@ -3896,10 +3417,10 @@
         <v>38932</v>
       </c>
       <c r="U6" s="16" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="W6" s="7" t="e">
         <v>#N/A</v>

--- a/scripts/files/COCO AU SHEET 16926.xlsx
+++ b/scripts/files/COCO AU SHEET 16926.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{587E2A93-2720-4B35-B7DE-B04CD48769AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33995A95-B65A-47D6-8ED6-078CA2226CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Property Name</t>
   </si>
@@ -45,7 +45,7 @@
     <t>SYSTEM ROOM NO</t>
   </si>
   <si>
-    <t>Coco Living AU</t>
+    <t>Coco | Au</t>
   </si>
 </sst>
 </file>
@@ -426,56 +426,23 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>9112683627</v>
+        <v>7358241985</v>
       </c>
       <c r="C2">
-        <v>511</v>
+        <v>204</v>
       </c>
       <c r="D2">
-        <v>512</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2">
-        <v>8669994544</v>
-      </c>
-      <c r="C3">
-        <v>512</v>
-      </c>
-      <c r="D3">
-        <v>511</v>
-      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:4" ht="20.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
-        <v>9022586799</v>
-      </c>
-      <c r="C4">
-        <v>402</v>
-      </c>
-      <c r="D4">
-        <v>204</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="20.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>7358241985</v>
-      </c>
-      <c r="C5">
-        <v>204</v>
-      </c>
-      <c r="D5">
-        <v>402</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scripts/files/COCO AU SHEET 16926.xlsx
+++ b/scripts/files/COCO AU SHEET 16926.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33995A95-B65A-47D6-8ED6-078CA2226CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE71881-C6FF-45AE-98F4-C6DF018DB425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,10 +429,10 @@
         <v>7358241985</v>
       </c>
       <c r="C2">
+        <v>109</v>
+      </c>
+      <c r="D2">
         <v>204</v>
-      </c>
-      <c r="D2">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.25">
